--- a/data/trans_camb/P1408-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1408-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>0,23</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,98; -1,68</t>
+          <t>-6,06; -1,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,64; -2,34</t>
+          <t>-6,72; -2,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 3,1</t>
+          <t>-2,86; 2,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,76; -0,88</t>
+          <t>-3,82; -0,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,78; -0,71</t>
+          <t>-3,77; -0,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 2,54</t>
+          <t>-0,88; 2,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,22; -1,78</t>
+          <t>-4,32; -1,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,71; -2,05</t>
+          <t>-4,53; -1,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 2,19</t>
+          <t>-1,36; 1,63</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>-2,7%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-58,88; -19,99</t>
+          <t>-59,74; -18,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-65,23; -27,79</t>
+          <t>-66,61; -25,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,65; 40,51</t>
+          <t>-28,69; 35,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-69,57; -23,8</t>
+          <t>-68,92; -21,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,8; -12,78</t>
+          <t>-70,59; -13,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,85; 67,94</t>
+          <t>-15,49; 70,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-58,32; -30,25</t>
+          <t>-59,54; -30,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-63,01; -33,38</t>
+          <t>-63,02; -31,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 38,92</t>
+          <t>-18,98; 27,23</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,86</t>
+          <t>-0,66</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,32</t>
+          <t>-0,11</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; -0,03</t>
+          <t>-1,83; -0,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 0,06</t>
+          <t>-1,67; 0,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,88; -0,07</t>
+          <t>-1,48; 0,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; -0,28</t>
+          <t>-1,74; -0,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,47; -0,05</t>
+          <t>-1,48; -0,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,17</t>
+          <t>-0,34; 1,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; -0,39</t>
+          <t>-1,57; -0,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,34; -0,21</t>
+          <t>-1,29; -0,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,34</t>
+          <t>-0,75; 0,47</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-40,06%</t>
+          <t>-31,0%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-17,29%</t>
+          <t>-5,9%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-68,95; 5,21</t>
+          <t>-69,47; -0,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-61,45; 6,76</t>
+          <t>-62,82; 2,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-66,25; -2,47</t>
+          <t>-54,48; 7,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-84,03; -18,64</t>
+          <t>-84,3; -18,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-72,55; -1,4</t>
+          <t>-72,04; 2,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,36; 106,73</t>
+          <t>-20,94; 115,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-70,8; -22,5</t>
+          <t>-70,17; -19,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-59,09; -11,65</t>
+          <t>-58,88; -5,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-41,48; 24,55</t>
+          <t>-33,49; 32,5</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,3</t>
+          <t>-0,37</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-0,25</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,73; -0,62</t>
+          <t>-2,59; -0,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 0,57</t>
+          <t>-1,87; 0,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,7</t>
+          <t>-1,58; 0,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,34; -0,0</t>
+          <t>-2,39; -0,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,46</t>
+          <t>-1,94; 0,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,95</t>
+          <t>-1,63; 0,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,01; -0,51</t>
+          <t>-2,05; -0,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 0,24</t>
+          <t>-1,61; 0,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,58</t>
+          <t>-1,18; 0,46</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-23,17%</t>
+          <t>-28,14%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-9,89%</t>
+          <t>-10,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-17,28%</t>
+          <t>-20,2%</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 147,83</t>
+          <t>-100,0; 170,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-74,02; 138,11</t>
+          <t>-73,7; 114,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1235,27 +1235,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 199,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-75,71; 233,54</t>
+          <t>-74,2; 196,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -26,89</t>
+          <t>-100,0; -39,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-83,85; 53,85</t>
+          <t>-85,22; 32,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-61,81; 81,36</t>
+          <t>-61,89; 74,84</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,72</t>
+          <t>-1,59</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,28</t>
+          <t>-0,13</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,99</t>
+          <t>-0,85</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,88; -1,14</t>
+          <t>-2,81; -1,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,03; -1,3</t>
+          <t>-3,09; -1,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,6; -0,91</t>
+          <t>-2,43; -0,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; -0,83</t>
+          <t>-2,19; -0,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,13; -0,74</t>
+          <t>-2,19; -0,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 0,47</t>
+          <t>-0,86; 0,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,29; -1,22</t>
+          <t>-2,33; -1,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,36; -1,23</t>
+          <t>-2,37; -1,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,63; -0,44</t>
+          <t>-1,43; -0,35</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-41,55%</t>
+          <t>-38,37%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-10,33%</t>
+          <t>-4,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-28,99%</t>
+          <t>-24,92%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-61,42; -31,06</t>
+          <t>-61,52; -29,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-65,09; -34,59</t>
+          <t>-65,81; -36,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-56,65; -24,99</t>
+          <t>-52,34; -19,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-69,53; -34,76</t>
+          <t>-70,06; -37,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-68,34; -31,39</t>
+          <t>-68,68; -32,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-34,66; 20,6</t>
+          <t>-27,22; 25,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-61,85; -39,07</t>
+          <t>-62,04; -39,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-62,54; -39,52</t>
+          <t>-62,58; -39,48</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-43,95; -14,1</t>
+          <t>-38,1; -10,73</t>
         </is>
       </c>
     </row>
